--- a/data/trans_orig/RUIDO_1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Provincia-trans_orig.xlsx
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>425</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>31840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32389</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59850</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70451</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>383</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>472</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22663</t>
+          <t>19549</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29149</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60318</t>
+          <t>60031</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75328</t>
+          <t>75529</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49742</t>
+          <t>49836</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>96291</t>
+          <t>97184</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>124882</t>
+          <t>124540</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>371</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>12707</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>24094</t>
+          <t>24643</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22875</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>29108</t>
+          <t>29006</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>41418</t>
+          <t>41570</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>21105</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>31258</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>45651</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>16735</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>22230</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>33126</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>25756</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>29588</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>38843</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>48060</t>
+          <t>48058</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>957</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -9455,12 +9455,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>516</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9470,12 +9470,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>6153</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>440</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13771</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>18522</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9922,12 +9922,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>19433</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>45266</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>39361</t>
+          <t>40156</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>55882</t>
+          <t>56722</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>77073</t>
+          <t>77336</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>98247</t>
+          <t>98195</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -11267,12 +11267,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>15748</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>21666</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -11380,12 +11380,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>43171</t>
+          <t>42459</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>52996</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>74493</t>
+          <t>75157</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>82613</t>
+          <t>82492</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11430,12 +11430,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11450,12 +11450,12 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>120377</t>
+          <t>121259</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>133408</t>
+          <t>133626</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -11610,12 +11610,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -11660,12 +11660,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -12175,12 +12175,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -12288,12 +12288,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -12338,12 +12338,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12358,12 +12358,12 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>29946</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12451,12 +12451,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -12514,12 +12514,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -12529,12 +12529,12 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -12549,12 +12549,12 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12584,12 +12584,12 @@
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>29390</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>52138</t>
+          <t>51265</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -12627,12 +12627,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>28156</t>
+          <t>27754</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>48959</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -12642,12 +12642,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -12662,12 +12662,12 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>32627</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>63226</t>
+          <t>60677</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -12677,12 +12677,12 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -12697,12 +12697,12 @@
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>66814</t>
+          <t>66152</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>100240</t>
+          <t>100004</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -12740,12 +12740,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>240776</t>
+          <t>242664</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>274374</t>
+          <t>275054</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -12755,12 +12755,12 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>268712</t>
+          <t>268513</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303444</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -12790,12 +12790,12 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>523082</t>
+          <t>519201</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>570088</t>
+          <t>569331</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3968</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>705</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1398,72 +1398,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3265</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>577</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>577</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1511,72 +1511,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1564</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>17,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4799</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>347</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -1737,82 +1737,82 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4639</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -1850,72 +1850,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24721</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31102</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>28963</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24878</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31840</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>26622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>47638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70940</t>
+          <t>56701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -1963,74 +1963,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>29033</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>29033</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>29033</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>42245</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>42245</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>42245</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>104</t>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2080,47 +2080,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6874</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4227</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -2193,47 +2193,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3911</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3444</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -2532,82 +2532,82 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>953</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5417</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>953</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -2645,47 +2645,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>4807</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>1241</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>5289</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,32 +2720,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>360</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -2758,72 +2758,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2282</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7196</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4971</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>845</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -2871,47 +2871,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2423</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1855</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>326</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>977</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>298</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2984,72 +2984,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3535</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7381</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3674</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>9418</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -3097,72 +3097,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4607</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>19371</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>35,53%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>5609</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>358</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -3210,72 +3210,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>38316</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>27443</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>44823</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>70,28%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>50,34%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>82,22%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>68889</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>60031</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>75529</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>76,62%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>37401</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>46530</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>111450</t>
+          <t>80811</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97184</t>
+          <t>68823</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>124540</t>
+          <t>88941</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>83,5%</t>
         </is>
       </c>
     </row>
@@ -3323,74 +3323,74 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>54515</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>54515</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>54515</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>78348</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>78348</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>78348</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>51996</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>51996</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>51996</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>60981</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>60981</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>60981</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>150</t>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -4344,72 +4344,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>3772</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>3833</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1316</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>7757</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>26,34%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -4457,72 +4457,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>6716</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>24,05%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>4596</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>2254</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>8807</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,22 +4532,22 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12707</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -4570,72 +4570,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>23312</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>19793</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>25667</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>83,49%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>70,88%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>21024</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>16468</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>24643</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>55,91%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>29006</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>47300</t>
+          <t>44323</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>41570</t>
+          <t>39317</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>52187</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -4683,74 +4683,74 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>27923</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>27923</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>27923</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>29453</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>29453</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>29453</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>28844</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>28844</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>28844</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>31427</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>31427</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>31427</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>99</t>
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>883</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -5478,72 +5478,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>8361</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>33,19%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>4415</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>9069</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>14,97%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>30,76%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -5704,72 +5704,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>11806</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>20,45%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>46,87%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>4310</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -5817,47 +5817,47 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>1458</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>20,25%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>779</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>4651</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>799</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>480</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -5930,72 +5930,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>15440</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>9763</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>20172</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>61,3%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>38,76%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>80,08%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>22558</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>17680</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>26456</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>59,97%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>89,73%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>27013</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>30391</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>44649</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -6043,74 +6043,74 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>29483</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>29483</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>29483</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>30159</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>30159</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>30159</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>26131</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>26131</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>26131</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>66</t>
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6951,72 +6951,72 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>2835</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>552</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>552</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,22 +7139,22 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -7177,72 +7177,72 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14594</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>10338</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>18253</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>52,99%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>37,54%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>66,27%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>13594</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>9589</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>16735</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>56,97%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>40,19%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>70,13%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>28780</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>33126</t>
+          <t>34027</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -7290,72 +7290,72 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>11845</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>16294</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>59,16%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>8639</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>5627</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>12169</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>51,0%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>25756</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -7403,74 +7403,74 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>27543</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>27543</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>27543</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>23862</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>23862</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>23862</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>24346</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>24346</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>24346</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>27328</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>27328</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>27328</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>97</t>
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -8198,82 +8198,82 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>873</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>5339</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>873</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -8311,72 +8311,72 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>2682</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>12,88%</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>582</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>582</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -8424,82 +8424,82 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>497</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -8537,72 +8537,72 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>4756</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>8738</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>29,96%</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>2406</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>5794</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>11,55%</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>27,82%</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>9889</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -8650,72 +8650,72 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>23045</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>18873</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>25785</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>79,0%</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>64,7%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>88,39%</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>17908</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>14539</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>19759</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>69,82%</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>94,89%</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>26231</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>29588</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>44139</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>39251</t>
+          <t>36381</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>48058</t>
+          <t>44647</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -8763,74 +8763,74 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>29170</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>29170</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>29170</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>20824</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>20824</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>20824</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>20655</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>20655</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>20655</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="P75" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>33320</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>33320</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>33320</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>87</t>
@@ -8838,17 +8838,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>366</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>860</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -9043,12 +9043,12 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -9106,82 +9106,82 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>4628</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
@@ -9191,12 +9191,12 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -9269,12 +9269,12 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>664</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
@@ -9304,12 +9304,12 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -9332,72 +9332,72 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>7773</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>4320</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>777</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>936</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -9450,67 +9450,67 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>2172</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>7969</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9520,32 +9520,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -9558,72 +9558,72 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>4369</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>9136</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>12,25%</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>2251</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>6043</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>757</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9633,32 +9633,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -9671,47 +9671,47 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>4553</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>3364</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>801</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,32 +9746,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>369</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -9784,72 +9784,72 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>3495</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>12421</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>4168</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>1614</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>8824</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -9897,72 +9897,72 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>7582</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>3763</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>12950</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>5013</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>9697</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>17,18%</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9972,32 +9972,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>18173</t>
+          <t>19690</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -10010,72 +10010,72 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>45597</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>37876</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>53272</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>61,14%</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>50,79%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>71,43%</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>39753</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>33312</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>45266</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>70,42%</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>59,01%</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>80,18%</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>48614</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>40156</t>
+          <t>30296</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>56722</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10085,32 +10085,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>88366</t>
+          <t>83116</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>77336</t>
+          <t>73969</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>98195</t>
+          <t>92859</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -10123,74 +10123,74 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>74577</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>74577</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>74577</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>56454</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>56454</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>56454</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>55092</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>55092</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>55092</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="P87" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>79644</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>79644</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>79644</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
           <t>175</t>
@@ -10198,17 +10198,17 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -11144,82 +11144,82 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>4146</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P96" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="Q96" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V96" s="2" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -11257,72 +11257,72 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>4471</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>1629</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>9849</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>9976</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>5923</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>16460</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11332,32 +11332,32 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>22698</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -11370,72 +11370,72 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>80443</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>74852</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>83528</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>48943</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>42459</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>52996</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>83,07%</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>72,06%</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>89,95%</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>79549</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>75157</t>
+          <t>44367</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>82492</t>
+          <t>54447</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11445,32 +11445,32 @@
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>128493</t>
+          <t>130561</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>121259</t>
+          <t>122920</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>133626</t>
+          <t>136366</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -11483,74 +11483,74 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>86025</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>86025</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>86025</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>58919</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>58919</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>58919</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>60644</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>60644</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>60644</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="P99" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>85074</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>85074</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>85074</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P99" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
           <t>201</t>
@@ -11558,17 +11558,17 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>146669</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>146669</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>146669</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -11600,72 +11600,72 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>9011</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>5694</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11675,22 +11675,22 @@
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V100" s="2" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -11713,72 +11713,72 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>5978</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>1538</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>4995</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11788,22 +11788,22 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -11826,82 +11826,82 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>4863</t>
-        </is>
-      </c>
-      <c r="N102" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P102" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q102" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -11979,7 +11979,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -11989,49 +11989,49 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P103" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q103" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R103" s="2" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="S103" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T103" s="2" t="inlineStr">
-        <is>
-          <t>2465</t>
-        </is>
-      </c>
-      <c r="U103" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -12052,72 +12052,72 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>3862</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>9542</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>5160</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12127,32 +12127,32 @@
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -12165,72 +12165,72 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>9340</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>3408</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>8622</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>3398</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>7611</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>9063</t>
-        </is>
-      </c>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12240,32 +12240,32 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -12278,72 +12278,72 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>9780</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>17711</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>8069</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>15478</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>21840</t>
+          <t>15867</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12353,32 +12353,32 @@
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>28049</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -12391,72 +12391,72 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>3502</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>9161</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>8930</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12466,17 +12466,17 @@
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -12504,72 +12504,72 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>21121</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>13849</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>29605</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>15930</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>10164</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>23670</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12579,32 +12579,32 @@
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>27282</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>51265</t>
+          <t>47878</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -12617,72 +12617,72 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>42107</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>32148</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>59117</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>8,98%</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>38289</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>27754</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>49269</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>11,55%</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>39583</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>32627</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>60677</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -12692,32 +12692,32 @@
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>81394</t>
+          <t>81691</t>
         </is>
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>66152</t>
+          <t>68681</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>100004</t>
+          <t>99951</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -12730,72 +12730,72 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>266611</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>249873</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>282316</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
           <t>351</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>256677</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>242664</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>275054</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>82,96%</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224681</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>211785</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>236506</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -12805,32 +12805,32 @@
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>544970</t>
+          <t>491292</t>
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>519201</t>
+          <t>469918</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>569331</t>
+          <t>509658</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -12843,74 +12843,74 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="O111" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="P111" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="M111" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="N111" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O111" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P111" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
           <t>979</t>
@@ -12918,17 +12918,17 @@
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
